--- a/Documentation/CTCSS.xlsx
+++ b/Documentation/CTCSS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m3n2bn\MPLABXProjects\CTCSSGen.X\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CD25D08-C363-4913-AE65-980EBB3D921A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA094EE-8069-4B81-A6B1-8F69448C6202}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8B806444-EB4C-413D-90EC-D2ABC0026D17}"/>
   </bookViews>
@@ -500,6 +500,57 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.41540099154272381"/>
+                  <c:y val="0.20276264321450874"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:cat>
             <c:strRef>
               <c:extLst>
@@ -1537,6 +1588,1042 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Freq(tone_sel)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1:$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2500000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Desired freq</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="2"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.45507022148547221"/>
+                  <c:y val="0.26270276316102886"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$A$4:$A$46</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Sheet1!$A$5:$A$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="42"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$5:$B$46</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Sheet1!$B$6:$B$46</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="41"/>
+                <c:pt idx="0">
+                  <c:v>69.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>71.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>74.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>79.7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>85.4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>88.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>91.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>94.8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>103.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>107.2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>110.9</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>114.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>118.8</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>127.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>131.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>136.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>141.30000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>146.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>151.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>156.69999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>162.19999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>167.9</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>173.8</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>179.9</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>186.2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>192.8</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>203.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>206.5</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>210.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>218.1</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>225.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>229.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>233.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>241.8</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>250.3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>254.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0184-4537-9930-1995F9A34A5E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="867141768"/>
+        <c:axId val="867135864"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$1:$D$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="4"/>
+                      <c:pt idx="0">
+                        <c:v>2500000</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>32</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Actual</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent4"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:trendline>
+                  <c:spPr>
+                    <a:ln w="19050" cap="rnd">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                      <a:prstDash val="sysDot"/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:trendlineType val="poly"/>
+                  <c:order val="2"/>
+                  <c:dispRSqr val="0"/>
+                  <c:dispEq val="1"/>
+                  <c:trendlineLbl>
+                    <c:layout>
+                      <c:manualLayout>
+                        <c:x val="-0.41540099154272381"/>
+                        <c:y val="0.20276264321450874"/>
+                      </c:manualLayout>
+                    </c:layout>
+                    <c:numFmt formatCode="General" sourceLinked="0"/>
+                    <c:spPr>
+                      <a:noFill/>
+                      <a:ln>
+                        <a:noFill/>
+                      </a:ln>
+                      <a:effectLst/>
+                    </c:spPr>
+                    <c:txPr>
+                      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                      <a:lstStyle/>
+                      <a:p>
+                        <a:pPr>
+                          <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="65000"/>
+                                <a:lumOff val="35000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:latin typeface="+mn-lt"/>
+                            <a:ea typeface="+mn-ea"/>
+                            <a:cs typeface="+mn-cs"/>
+                          </a:defRPr>
+                        </a:pPr>
+                        <a:endParaRPr lang="en-US"/>
+                      </a:p>
+                    </c:txPr>
+                  </c:trendlineLbl>
+                </c:trendline>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Sheet1!$A$4:$A$46</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$5:$A$46</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="42"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>9</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>10</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>11</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>13</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>14</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>17</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>18</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>19</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>20</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>21</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>22</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>24</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>25</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>27</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>28</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>30</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>31</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>32</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>33</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>34</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>35</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>36</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>37</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>38</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>39</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>40</c:v>
+                      </c:pt>
+                      <c:pt idx="41">
+                        <c:v>41</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:fullRef>
+                          <c15:sqref>Sheet1!$D$5:$D$46</c15:sqref>
+                        </c15:fullRef>
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$D$6:$D$46</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="41"/>
+                      <c:pt idx="0">
+                        <c:v>69.321206743566989</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>71.938305709023936</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>74.404761904761898</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>77.046351084812628</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>79.719387755102048</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>82.584566596194506</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>85.47592997811816</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>88.577097505668931</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>91.588511137162953</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>94.8118932038835</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>97.412718204488783</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>100.03201024327785</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>103.61405835543766</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>107.31456043956044</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>110.97301136363636</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>114.88970588235294</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>118.91171993911721</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>123.03149606299213</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>127.44698205546493</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>131.96790540540542</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>136.58216783216784</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>141.53079710144928</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>146.30149812734084</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>151.40503875968992</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>156.87751004016064</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>162.42203742203742</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>168.01075268817203</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>173.99777282850781</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>180.0115207373272</c:v>
+                      </c:pt>
+                      <c:pt idx="29">
+                        <c:v>186.45584725536992</c:v>
+                      </c:pt>
+                      <c:pt idx="30">
+                        <c:v>192.90123456790124</c:v>
+                      </c:pt>
+                      <c:pt idx="31">
+                        <c:v>203.98172323759792</c:v>
+                      </c:pt>
+                      <c:pt idx="32">
+                        <c:v>206.67989417989418</c:v>
+                      </c:pt>
+                      <c:pt idx="33">
+                        <c:v>211.14864864864865</c:v>
+                      </c:pt>
+                      <c:pt idx="34">
+                        <c:v>218.22625698324023</c:v>
+                      </c:pt>
+                      <c:pt idx="35">
+                        <c:v>225.79479768786126</c:v>
+                      </c:pt>
+                      <c:pt idx="36">
+                        <c:v>229.10557184750732</c:v>
+                      </c:pt>
+                      <c:pt idx="37">
+                        <c:v>233.90718562874252</c:v>
+                      </c:pt>
+                      <c:pt idx="38">
+                        <c:v>241.87306501547988</c:v>
+                      </c:pt>
+                      <c:pt idx="39">
+                        <c:v>250.40064102564102</c:v>
+                      </c:pt>
+                      <c:pt idx="40">
+                        <c:v>254.47882736156353</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-0184-4537-9930-1995F9A34A5E}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="867141768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="867135864"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="867135864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="867141768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1743,7 +2830,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2291,6 +3378,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -3324,7 +4451,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3432,6 +4559,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3442,6 +4574,11 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -3473,6 +4610,9 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3827,6 +4967,509 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4411,6 +6054,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>52388</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2943AAB-67E5-48DB-B029-A37AAF2DC28D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
